--- a/Ozrit HR data/ozrit/HR/Salary/Paysheets/Paysheet September.xlsx
+++ b/Ozrit HR data/ozrit/HR/Salary/Paysheets/Paysheet September.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\Salary\Paysheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E458CB33-2984-4326-9149-8F3175B77A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF90522-C67A-45F7-A3C2-3858EDD6C475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$46</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="249">
   <si>
     <t>EMP Code</t>
   </si>
@@ -588,112 +588,193 @@
     <t>Pusuluri Sai Sanjana</t>
   </si>
   <si>
+    <t>sanjana@ozrit.com</t>
+  </si>
+  <si>
+    <t>SBIN0008493</t>
+  </si>
+  <si>
+    <t>+91 95503 39195</t>
+  </si>
+  <si>
+    <t>Veeresha S</t>
+  </si>
+  <si>
+    <t>Node js Trainee</t>
+  </si>
+  <si>
+    <t>SBIN0011267</t>
+  </si>
+  <si>
+    <t>+91 6360 846 104</t>
+  </si>
+  <si>
+    <t>Digtial Marketing Intern</t>
+  </si>
+  <si>
+    <t>SURLA LAKSHMANUDU</t>
+  </si>
+  <si>
+    <t>Lakshman@ozrit.com</t>
+  </si>
+  <si>
+    <t>Angular Developer</t>
+  </si>
+  <si>
+    <t>Mahendrakar Raghavendra Nath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Marketing Lead </t>
+  </si>
+  <si>
+    <t>raghavendra@ozrit.com</t>
+  </si>
+  <si>
+    <t>ICIC0001941</t>
+  </si>
+  <si>
+    <t>PRAMODKUMAR BONTHU</t>
+  </si>
+  <si>
+    <t>+91 92814 82485</t>
+  </si>
+  <si>
+    <t>SBIN0021323</t>
+  </si>
+  <si>
+    <t>Pramod@ozrit.in</t>
+  </si>
+  <si>
+    <t>veersha@ozrit.in</t>
+  </si>
+  <si>
+    <t>raghu@ozrit.in</t>
+  </si>
+  <si>
+    <t>venkatesh@ozrit.in</t>
+  </si>
+  <si>
+    <t>sireesha@ozrit.in</t>
+  </si>
+  <si>
+    <t>kiran@ozrit.in</t>
+  </si>
+  <si>
+    <t>sharan@ozrit.in</t>
+  </si>
+  <si>
+    <t>yuvraj@ozrit.in</t>
+  </si>
+  <si>
+    <t>neelesh@ozrit.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marri Chandra Mohan </t>
+  </si>
+  <si>
+    <t>+91 93984 10571</t>
+  </si>
+  <si>
+    <t>SBIN0002696</t>
+  </si>
+  <si>
+    <t>chandramohan@ozrit.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total </t>
+  </si>
+  <si>
+    <t>+91 76808 01983</t>
+  </si>
+  <si>
+    <t>KARRE VAMSI KRISHNA</t>
+  </si>
+  <si>
+    <t> UBIN0830259</t>
+  </si>
+  <si>
     <t>Digital Marketing Executive</t>
   </si>
   <si>
-    <t>sanjana@ozrit.com</t>
-  </si>
-  <si>
-    <t>SBIN0008493</t>
-  </si>
-  <si>
-    <t>+91 95503 39195</t>
-  </si>
-  <si>
-    <t>Veeresha S</t>
-  </si>
-  <si>
-    <t>Node js Trainee</t>
-  </si>
-  <si>
-    <t>SBIN0011267</t>
-  </si>
-  <si>
-    <t>+91 6360 846 104</t>
-  </si>
-  <si>
-    <t>Digtial Marketing Intern</t>
-  </si>
-  <si>
-    <t>SURLA LAKSHMANUDU</t>
-  </si>
-  <si>
-    <t>Lakshman@ozrit.com</t>
-  </si>
-  <si>
-    <t>Angular Developer</t>
-  </si>
-  <si>
-    <t>Mahendrakar Raghavendra Nath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing Lead </t>
-  </si>
-  <si>
-    <t>raghavendra@ozrit.com</t>
-  </si>
-  <si>
-    <t>ICIC0001941</t>
-  </si>
-  <si>
-    <t>PRAMODKUMAR BONTHU</t>
-  </si>
-  <si>
-    <t>+91 92814 82485</t>
-  </si>
-  <si>
-    <t>SBIN0021323</t>
-  </si>
-  <si>
-    <t>Pramod@ozrit.in</t>
-  </si>
-  <si>
-    <t>veersha@ozrit.in</t>
-  </si>
-  <si>
-    <t>raghu@ozrit.in</t>
-  </si>
-  <si>
-    <t>venkatesh@ozrit.in</t>
-  </si>
-  <si>
-    <t>sireesha@ozrit.in</t>
-  </si>
-  <si>
-    <t>kiran@ozrit.in</t>
-  </si>
-  <si>
-    <t>sharan@ozrit.in</t>
-  </si>
-  <si>
-    <t>yuvraj@ozrit.in</t>
-  </si>
-  <si>
-    <t>neelesh@ozrit.in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marri Chandra Mohan </t>
-  </si>
-  <si>
-    <t>+91 93984 10571</t>
-  </si>
-  <si>
-    <t>SBIN0002696</t>
-  </si>
-  <si>
-    <t>chandramohan@ozrit.in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total </t>
-  </si>
-  <si>
-    <t>+91 76808 01983</t>
-  </si>
-  <si>
-    <t>KARRE VAMSI KRISHNA</t>
-  </si>
-  <si>
-    <t> UBIN0830259</t>
+    <t>013</t>
+  </si>
+  <si>
+    <t>Pilli Vishwanth</t>
+  </si>
+  <si>
+    <t>Vishwanth@ozrit.com</t>
+  </si>
+  <si>
+    <t>91 91006 99875</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>BIKKINA MOUNIKA PRIYA</t>
+  </si>
+  <si>
+    <t>mounikapriya@ozrit.com</t>
+  </si>
+  <si>
+    <t>91 96666 05466</t>
+  </si>
+  <si>
+    <t>AXIS</t>
+  </si>
+  <si>
+    <t>UTIB0002744</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Sri Kumar Manikanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full stack developer </t>
+  </si>
+  <si>
+    <t>manikantak@ozrit.com</t>
+  </si>
+  <si>
+    <t>91 6305 889568</t>
+  </si>
+  <si>
+    <t>UTIB0000553</t>
+  </si>
+  <si>
+    <t>PHANI KUMAR KAVULA</t>
+  </si>
+  <si>
+    <t>phanikumar@ozrit.com</t>
+  </si>
+  <si>
+    <t>91 6309 806295</t>
+  </si>
+  <si>
+    <t>SBIN0010102</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Shaik Asif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr.PHP developer </t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Asif@ozrit.com</t>
+  </si>
+  <si>
+    <t>91 89192 73834</t>
+  </si>
+  <si>
+    <t>HDFC0004189</t>
   </si>
 </sst>
 </file>
@@ -703,7 +784,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -759,8 +840,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -773,8 +873,20 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -899,12 +1011,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1044,9 +1167,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1066,6 +1186,111 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1349,14 +1574,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X55"/>
+  <dimension ref="A1:X85"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" style="1"/>
     <col min="2" max="2" width="59.08984375" style="1" customWidth="1"/>
     <col min="3" max="4" width="44.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46" style="25" customWidth="1"/>
-    <col min="6" max="6" width="46" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46" style="25" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="46" style="1" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="35.1796875" style="25" customWidth="1"/>
     <col min="8" max="8" width="26.08984375" style="26" customWidth="1"/>
     <col min="9" max="9" width="14.453125" style="22" customWidth="1"/>
@@ -1432,16 +1657,16 @@
       <c r="G2" s="13">
         <v>50100707596631</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="47" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="14">
         <v>24208</v>
       </c>
       <c r="J2" s="32"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
@@ -1465,1548 +1690,1788 @@
       <c r="G3" s="13">
         <v>50100707596571</v>
       </c>
-      <c r="H3" s="48" t="s">
+      <c r="H3" s="47" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="14">
         <v>26920</v>
       </c>
       <c r="J3" s="32"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-    </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="K3" s="56"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="52"/>
+    </row>
+    <row r="4" spans="1:24" s="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="66" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="13">
-        <v>50100740182030</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="14">
-        <v>29632</v>
-      </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
+      <c r="G4" s="69">
+        <v>50100103657928</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>248</v>
+      </c>
+      <c r="I4" s="71">
+        <v>48042</v>
+      </c>
+      <c r="J4" s="72"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="74"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>50100740182247</v>
-      </c>
-      <c r="H5" s="48" t="s">
+        <v>50100740182030</v>
+      </c>
+      <c r="H5" s="47" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="14">
-        <v>32073</v>
+        <v>29632</v>
       </c>
       <c r="J5" s="32"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="52"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="13">
-        <v>50100740182069</v>
-      </c>
-      <c r="H6" s="48" t="s">
+        <v>50100740182247</v>
+      </c>
+      <c r="H6" s="47" t="s">
         <v>25</v>
       </c>
       <c r="I6" s="14">
-        <v>29632</v>
+        <v>32073</v>
       </c>
       <c r="J6" s="32"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="52"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>110118215033</v>
-      </c>
-      <c r="H7" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="23">
-        <v>18599</v>
+        <v>50100740182069</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="14">
+        <v>29632</v>
       </c>
       <c r="J7" s="32"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="52"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="13">
+        <v>110118215033</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="23">
+        <v>18599</v>
+      </c>
+      <c r="J8" s="32"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="52"/>
+    </row>
+    <row r="9" spans="1:24" s="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="69">
+        <v>50100810418075</v>
+      </c>
+      <c r="H9" s="70" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="77">
+        <v>22704</v>
+      </c>
+      <c r="J9" s="78"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="74"/>
+    </row>
+    <row r="10" spans="1:24" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B10" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D10" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="13">
-        <v>50100740181906</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="14">
-        <v>26920</v>
-      </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-    </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="13">
-        <v>50100707596427</v>
-      </c>
-      <c r="H9" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="14">
-        <v>24208</v>
-      </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-    </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="13">
-        <v>50100707596430</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="14">
-        <v>46200</v>
+        <v>50100740181906</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="54">
+        <v>48700</v>
       </c>
       <c r="J10" s="32"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="52"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="13">
-        <v>50100766581478</v>
-      </c>
-      <c r="H11" s="48" t="s">
-        <v>142</v>
+        <v>50100707596427</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="I11" s="14">
-        <v>17130</v>
+        <v>24208</v>
       </c>
       <c r="J11" s="32"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="52"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>62</v>
+        <v>52</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>63</v>
+        <v>54</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="13">
-        <v>50100810416757</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>25</v>
+        <v>50100707596430</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="I12" s="14">
-        <v>12810</v>
+        <v>46200</v>
       </c>
       <c r="J12" s="32"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="52"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="13">
-        <v>50100800585883</v>
-      </c>
-      <c r="H13" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="23">
-        <v>10507</v>
+        <v>50100766581478</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="14">
+        <v>17130</v>
       </c>
       <c r="J13" s="32"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="52"/>
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G14" s="13">
-        <v>50100810417902</v>
-      </c>
-      <c r="H14" s="48" t="s">
+        <v>50100810416757</v>
+      </c>
+      <c r="H14" s="47" t="s">
         <v>25</v>
       </c>
       <c r="I14" s="14">
-        <v>11232</v>
+        <v>12810</v>
       </c>
       <c r="J14" s="32"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="52"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="20">
-        <v>50100810417276</v>
-      </c>
-      <c r="H15" s="49" t="s">
+      <c r="G15" s="13">
+        <v>50100800585883</v>
+      </c>
+      <c r="H15" s="47" t="s">
         <v>25</v>
       </c>
       <c r="I15" s="23">
-        <v>12096</v>
+        <v>10507</v>
       </c>
       <c r="J15" s="32"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="52"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>156</v>
+      <c r="D16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="21">
-        <v>50100810418559</v>
-      </c>
-      <c r="H16" s="50" t="s">
+      <c r="G16" s="13">
+        <v>50100810417902</v>
+      </c>
+      <c r="H16" s="47" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="14">
         <v>11232</v>
       </c>
       <c r="J16" s="32"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="52"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>83</v>
+      <c r="A17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="21">
-        <v>50100809700685</v>
-      </c>
-      <c r="H17" s="50" t="s">
+      <c r="G17" s="20">
+        <v>50100810417276</v>
+      </c>
+      <c r="H17" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="23">
         <v>12096</v>
       </c>
       <c r="J17" s="32"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="52"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="21">
-        <v>50100810418177</v>
-      </c>
-      <c r="H18" s="50" t="s">
+        <v>50100810418559</v>
+      </c>
+      <c r="H18" s="49" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>20592</v>
+        <v>11232</v>
       </c>
       <c r="J18" s="32"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K18" s="56"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="52"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="21">
-        <v>50100762090454</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>92</v>
+        <v>50100809700685</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>25</v>
       </c>
       <c r="I19" s="14">
-        <v>11232</v>
+        <v>12096</v>
       </c>
       <c r="J19" s="32"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K19" s="56"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="52"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>96</v>
+        <v>84</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="21">
-        <v>50100810417020</v>
-      </c>
-      <c r="H20" s="50" t="s">
+        <v>50100810418177</v>
+      </c>
+      <c r="H20" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="23">
-        <v>12810</v>
+      <c r="I20" s="14">
+        <v>20592</v>
       </c>
       <c r="J20" s="32"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
+      <c r="K20" s="56"/>
+      <c r="L20" s="64"/>
+      <c r="M20" s="52"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="27" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="21">
-        <v>50100690505647</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>102</v>
+        <v>50100762090454</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>92</v>
       </c>
       <c r="I21" s="14">
-        <v>14279</v>
+        <v>11232</v>
       </c>
       <c r="J21" s="32"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="21">
-        <v>50100810417977</v>
-      </c>
-      <c r="H22" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="23">
-        <v>11232</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="21">
-        <v>50100810416846</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="23">
-        <v>12810</v>
-      </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="52"/>
+    </row>
+    <row r="22" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="80" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" s="81" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="82" t="s">
+        <v>228</v>
+      </c>
+      <c r="E22" s="81" t="s">
+        <v>229</v>
+      </c>
+      <c r="F22" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="G22" s="83">
+        <v>923010005234687</v>
+      </c>
+      <c r="H22" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="I22" s="85">
+        <v>17355</v>
+      </c>
+      <c r="J22" s="86"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="74"/>
+    </row>
+    <row r="23" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="87" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>234</v>
+      </c>
+      <c r="D23" s="82" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" s="81" t="s">
+        <v>236</v>
+      </c>
+      <c r="F23" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="G23" s="83">
+        <v>922010060268217</v>
+      </c>
+      <c r="H23" s="84" t="s">
+        <v>237</v>
+      </c>
+      <c r="I23" s="88">
+        <v>46200</v>
+      </c>
+      <c r="J23" s="86"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="74"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="27" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G24" s="21">
-        <v>50100810418329</v>
-      </c>
-      <c r="H24" s="50" t="s">
+        <v>50100810417020</v>
+      </c>
+      <c r="H24" s="49" t="s">
         <v>25</v>
       </c>
       <c r="I24" s="23">
         <v>12810</v>
       </c>
       <c r="J24" s="32"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="53"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="52"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>150</v>
+      <c r="A25" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>93</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G25" s="21">
-        <v>50100810416935</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" s="23">
-        <v>12810</v>
+        <v>50100690505647</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="14">
+        <v>14279</v>
       </c>
       <c r="J25" s="32"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="53"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="64"/>
+      <c r="M25" s="52"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>117</v>
+      <c r="A26" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>104</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G26" s="21">
-        <v>50100728574951</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" s="14">
-        <v>17130</v>
+        <v>50100810417977</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="23">
+        <v>11232</v>
       </c>
       <c r="J26" s="32"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="53"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="52"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A27" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>121</v>
+      <c r="A27" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>107</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="21">
-        <v>50100771632300</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="I27" s="14">
-        <v>14408</v>
+        <v>50100810416846</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="23">
+        <v>12810</v>
       </c>
       <c r="J27" s="32"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="53"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="64"/>
+      <c r="M27" s="52"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" s="32" t="s">
-        <v>125</v>
+      <c r="A28" s="27" t="s">
+        <v>110</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="21">
-        <v>50100827377098</v>
-      </c>
-      <c r="H28" s="50" t="s">
+        <v>50100810418329</v>
+      </c>
+      <c r="H28" s="49" t="s">
         <v>25</v>
       </c>
       <c r="I28" s="23">
-        <v>19688</v>
+        <v>12810</v>
       </c>
       <c r="J28" s="32"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="53"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="64"/>
+      <c r="M28" s="52"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A29" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" s="25">
-        <v>918309088366</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G29" s="25">
-        <v>194101509938</v>
-      </c>
-      <c r="H29" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="I29" s="14">
-        <v>55539</v>
-      </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
+      <c r="A29" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="21">
+        <v>50100810416935</v>
+      </c>
+      <c r="H29" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="23">
+        <v>12810</v>
+      </c>
+      <c r="J29" s="32"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="52"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A30" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>195</v>
+      <c r="A30" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="21">
-        <v>919398286957</v>
+        <v>28</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="21">
-        <v>50100833441352</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="23">
-        <v>35342</v>
+        <v>50100728574951</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="14">
+        <v>17130</v>
       </c>
       <c r="J30" s="32"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="53"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="52"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>176</v>
+      <c r="A31" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>121</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="D31" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="21">
-        <v>919032232603</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G31" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="I31" s="23">
-        <v>11715</v>
+        <v>122</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="21">
+        <v>50100771632300</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="14">
+        <v>14408</v>
       </c>
       <c r="J31" s="32"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="53"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="64"/>
+      <c r="M31" s="52"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>185</v>
+        <v>125</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="44" t="s">
-        <v>187</v>
+        <v>28</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F32" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="21">
+        <v>50100827377098</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" s="23">
+        <v>19688</v>
+      </c>
+      <c r="J32" s="32"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="52"/>
+    </row>
+    <row r="33" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="86" t="s">
+        <v>242</v>
+      </c>
+      <c r="B33" s="89" t="s">
+        <v>238</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="82" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>240</v>
+      </c>
+      <c r="F33" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="G32" s="21">
-        <v>39923398991</v>
-      </c>
-      <c r="H32" s="50" t="s">
-        <v>188</v>
-      </c>
-      <c r="I32" s="23">
-        <v>8173</v>
-      </c>
-      <c r="J32" s="32"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="53"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A33" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="21">
-        <v>50100811327863</v>
-      </c>
-      <c r="H33" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="I33" s="23">
-        <v>7000</v>
-      </c>
-      <c r="J33" s="32"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="53"/>
+      <c r="G33" s="89">
+        <v>40523895192</v>
+      </c>
+      <c r="H33" s="89" t="s">
+        <v>241</v>
+      </c>
+      <c r="I33" s="90">
+        <v>70688</v>
+      </c>
+      <c r="J33" s="91"/>
+      <c r="K33" s="92"/>
+      <c r="L33" s="74"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E34" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="F34" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" s="34">
-        <v>128212010003688</v>
-      </c>
-      <c r="H34" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="I34" s="23">
-        <v>14850</v>
-      </c>
-      <c r="J34" s="32"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="53"/>
+      <c r="A34" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="25">
+        <v>918309088366</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" s="25">
+        <v>194101509938</v>
+      </c>
+      <c r="H34" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="I34" s="14">
+        <v>55539</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="52"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>135</v>
+        <v>174</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D35" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>167</v>
+        <v>196</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="E35" s="21">
+        <v>919398286957</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="G35" s="21">
-        <v>4449577840</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="I35" s="14">
-        <v>4758</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="53"/>
+        <v>50100833441352</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I35" s="23">
+        <v>35342</v>
+      </c>
+      <c r="J35" s="32"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="52"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>137</v>
+        <v>175</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>176</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="21">
-        <v>50100691742492</v>
-      </c>
-      <c r="H36" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="14">
-        <v>5000</v>
-      </c>
-      <c r="J36" s="40"/>
-      <c r="K36" s="53"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="53"/>
+        <v>178</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="21">
+        <v>919032232603</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="I36" s="23">
+        <v>11715</v>
+      </c>
+      <c r="J36" s="32"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="52"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>149</v>
+        <v>177</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" s="45" t="s">
-        <v>211</v>
+        <v>221</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>186</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="G37" s="21">
-        <v>50100827376912</v>
-      </c>
-      <c r="H37" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I37" s="14">
-        <v>4677</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="53"/>
+        <v>39923398991</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" s="23">
+        <v>8173</v>
+      </c>
+      <c r="J37" s="32"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="52"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>143</v>
+      <c r="B38" s="33" t="s">
+        <v>154</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D38" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="G38" s="24">
-        <v>223201001139</v>
-      </c>
-      <c r="H38" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" s="14">
-        <v>4919</v>
-      </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="53"/>
+        <v>86</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="21">
+        <v>50100811327863</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38" s="23">
+        <v>7000</v>
+      </c>
+      <c r="J38" s="32"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="52"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="24">
-        <v>37662822583</v>
+        <v>129</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="34">
+        <v>128212010003688</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="I39" s="14">
-        <v>5000</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
+        <v>133</v>
+      </c>
+      <c r="I39" s="23">
+        <v>14850</v>
+      </c>
+      <c r="J39" s="32"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="52"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>134</v>
       </c>
       <c r="D40" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G40" s="24">
-        <v>4175101002881</v>
-      </c>
-      <c r="H40" s="50" t="s">
-        <v>147</v>
+        <v>212</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" s="21">
+        <v>4449577840</v>
+      </c>
+      <c r="H40" s="49" t="s">
+        <v>136</v>
       </c>
       <c r="I40" s="14">
         <v>4758</v>
       </c>
       <c r="J40" s="14"/>
-      <c r="K40" s="53"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="53"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="52"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>134</v>
       </c>
       <c r="D41" s="45" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="G41" s="21">
-        <v>50100565128982</v>
-      </c>
-      <c r="H41" s="50" t="s">
-        <v>142</v>
+        <v>50100691742492</v>
+      </c>
+      <c r="H41" s="49" t="s">
+        <v>138</v>
       </c>
       <c r="I41" s="14">
         <v>5000</v>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="61"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="52"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="D42" s="45" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="G42" s="21">
-        <v>62447891496</v>
-      </c>
-      <c r="H42" s="50" t="s">
-        <v>192</v>
+        <v>50100827376912</v>
+      </c>
+      <c r="H42" s="49" t="s">
+        <v>25</v>
       </c>
       <c r="I42" s="14">
-        <v>1452</v>
+        <v>4677</v>
       </c>
       <c r="J42" s="14"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="53"/>
+      <c r="K42" s="61"/>
+      <c r="L42" s="64"/>
+      <c r="M42" s="52"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="D43" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>215</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G43" s="21">
-        <v>35924814070</v>
-      </c>
-      <c r="H43" s="50" t="s">
-        <v>216</v>
+        <v>209</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="G43" s="24">
+        <v>223201001139</v>
+      </c>
+      <c r="H43" s="49" t="s">
+        <v>144</v>
       </c>
       <c r="I43" s="14">
-        <v>1935</v>
+        <v>4919</v>
       </c>
       <c r="J43" s="14"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="53"/>
+      <c r="K43" s="62"/>
+      <c r="L43" s="64"/>
+      <c r="M43" s="52"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>220</v>
+      <c r="B44" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="G44" s="21">
-        <v>302510100011234</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>221</v>
+      <c r="D44" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="24">
+        <v>37662822583</v>
+      </c>
+      <c r="H44" s="49" t="s">
+        <v>148</v>
       </c>
       <c r="I44" s="14">
-        <v>2419</v>
+        <v>5000</v>
       </c>
       <c r="J44" s="14"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="53"/>
+      <c r="K44" s="62"/>
+      <c r="L44" s="64"/>
+      <c r="M44" s="52"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>134</v>
       </c>
       <c r="D45" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G45" s="24">
+        <v>4175101002881</v>
+      </c>
+      <c r="H45" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="I45" s="14">
+        <v>4758</v>
+      </c>
+      <c r="J45" s="14"/>
+      <c r="K45" s="62"/>
+      <c r="L45" s="64"/>
+      <c r="M45" s="52"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A46" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="21">
+        <v>50100565128982</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="I46" s="14">
+        <v>5000</v>
+      </c>
+      <c r="J46" s="14"/>
+      <c r="K46" s="62"/>
+      <c r="L46" s="64"/>
+      <c r="M46" s="52"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A47" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D47" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E47" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G47" s="21">
+        <v>62447891496</v>
+      </c>
+      <c r="H47" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I47" s="14">
+        <v>1452</v>
+      </c>
+      <c r="J47" s="14"/>
+      <c r="K47" s="62"/>
+      <c r="L47" s="64"/>
+      <c r="M47" s="52"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A48" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="21">
+        <v>35924814070</v>
+      </c>
+      <c r="H48" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="I48" s="14">
+        <v>1935</v>
+      </c>
+      <c r="J48" s="14"/>
+      <c r="K48" s="62"/>
+      <c r="L48" s="64"/>
+      <c r="M48" s="52"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A49" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="G49" s="21">
+        <v>302510100011234</v>
+      </c>
+      <c r="H49" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="I49" s="14">
+        <v>2419</v>
+      </c>
+      <c r="J49" s="14"/>
+      <c r="K49" s="62"/>
+      <c r="L49" s="64"/>
+      <c r="M49" s="52"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A50" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="21">
+        <v>36094134370</v>
+      </c>
+      <c r="H50" s="49" t="s">
         <v>203</v>
       </c>
-      <c r="F45" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G45" s="21">
-        <v>36094134370</v>
-      </c>
-      <c r="H45" s="50" t="s">
-        <v>204</v>
-      </c>
-      <c r="I45" s="14">
+      <c r="I50" s="14">
         <v>645</v>
       </c>
-      <c r="J45" s="14"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="53"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="I46" s="36">
-        <f>SUM(I2:I45)</f>
-        <v>678478</v>
-      </c>
-      <c r="J46" s="14"/>
-      <c r="K46" s="53"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="53"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="50"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="53"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="53"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="53"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F50" s="41"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
-      <c r="M50" s="53"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="64"/>
+      <c r="M50" s="52"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="F51" s="41"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
-      <c r="M51" s="53"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="I51" s="36">
+        <f>SUM(I2:I50)</f>
+        <v>905247</v>
+      </c>
+      <c r="J51" s="14"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="64"/>
+      <c r="M51" s="52"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K52" s="53"/>
-      <c r="L52" s="53"/>
-      <c r="M52" s="53"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="64"/>
+      <c r="M52" s="52"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K53" s="53"/>
-      <c r="L53" s="53"/>
-      <c r="M53" s="53"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="64"/>
+      <c r="M53" s="52"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="64"/>
+      <c r="M54" s="52"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="K55" s="53"/>
-      <c r="L55" s="53"/>
-      <c r="M55" s="53"/>
+      <c r="F55" s="41"/>
+      <c r="K55" s="52"/>
+      <c r="L55" s="64"/>
+      <c r="M55" s="52"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="F56" s="41"/>
+      <c r="K56" s="52"/>
+      <c r="L56" s="64"/>
+      <c r="M56" s="52"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K57" s="52"/>
+      <c r="L57" s="64"/>
+      <c r="M57" s="52"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K58" s="52"/>
+      <c r="L58" s="64"/>
+      <c r="M58" s="52"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K59" s="52"/>
+      <c r="L59" s="64"/>
+      <c r="M59" s="52"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="K60" s="52"/>
+      <c r="L60" s="64"/>
+      <c r="M60" s="52"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L61" s="64"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L62" s="64"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L63" s="64"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L64" s="64"/>
+    </row>
+    <row r="65" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L65" s="64"/>
+    </row>
+    <row r="66" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L66" s="64"/>
+    </row>
+    <row r="67" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L67" s="64"/>
+    </row>
+    <row r="68" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L68" s="64"/>
+    </row>
+    <row r="69" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L69" s="64"/>
+    </row>
+    <row r="70" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L70" s="64"/>
+    </row>
+    <row r="71" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L71" s="64"/>
+    </row>
+    <row r="72" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L72" s="64"/>
+    </row>
+    <row r="73" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L73" s="64"/>
+    </row>
+    <row r="74" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L74" s="64"/>
+    </row>
+    <row r="75" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L75" s="64"/>
+    </row>
+    <row r="76" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L76" s="64"/>
+    </row>
+    <row r="77" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L77" s="64"/>
+    </row>
+    <row r="78" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L78" s="64"/>
+    </row>
+    <row r="79" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L79" s="64"/>
+    </row>
+    <row r="80" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L80" s="64"/>
+    </row>
+    <row r="81" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L81" s="64"/>
+    </row>
+    <row r="82" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L82" s="64"/>
+    </row>
+    <row r="83" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L83" s="64"/>
+    </row>
+    <row r="84" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L84" s="64"/>
+    </row>
+    <row r="85" spans="12:12" x14ac:dyDescent="0.35">
+      <c r="L85" s="64"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X41" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="D26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="D27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="D33" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D34" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="D10" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D35" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="D36" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D37" r:id="rId32" xr:uid="{F65D468A-5ADE-4DBD-B37A-288BC47159EC}"/>
-    <hyperlink ref="D38" r:id="rId33" xr:uid="{03E03F3D-EA98-4CB2-B14A-65622FBEA0B4}"/>
-    <hyperlink ref="D39" r:id="rId34" xr:uid="{98A0C304-CAF0-41EF-B1EA-BF07537A4730}"/>
-    <hyperlink ref="D40" r:id="rId35" xr:uid="{A3E5F334-B5CE-4AEE-A42F-A5A17D96742A}"/>
-    <hyperlink ref="D31" r:id="rId36" xr:uid="{E447C236-D2AB-4A20-B7C1-8591FA3BE211}"/>
-    <hyperlink ref="D41" r:id="rId37" xr:uid="{6BB870EC-F64E-4BA7-8065-EB3402974981}"/>
-    <hyperlink ref="D32" r:id="rId38" xr:uid="{9D31C861-653F-4F2A-884C-44664722875D}"/>
-    <hyperlink ref="D42" r:id="rId39" xr:uid="{D3C33CAD-BAA3-447A-AF42-A156E65BC35D}"/>
-    <hyperlink ref="D30" r:id="rId40" xr:uid="{90D635D6-A4E8-4BE4-B7D4-67E3C59A2CEC}"/>
-    <hyperlink ref="D29" r:id="rId41" xr:uid="{50B70E74-0596-4624-AAA8-4F7F63D093DF}"/>
-    <hyperlink ref="D45" r:id="rId42" xr:uid="{B5312202-AB22-4CBA-AFB1-BA400ED0C6AD}"/>
-    <hyperlink ref="D44" r:id="rId43" xr:uid="{99DB107E-7511-46F5-A50B-F0E54A20B7BB}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="D14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="D17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="D18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="D20" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="D21" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="D24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="D25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="D26" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="D27" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="D28" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="D29" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="D30" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="D31" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="D32" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="D38" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="D39" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="D12" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="D40" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="D41" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="D42" r:id="rId32" xr:uid="{F65D468A-5ADE-4DBD-B37A-288BC47159EC}"/>
+    <hyperlink ref="D43" r:id="rId33" xr:uid="{03E03F3D-EA98-4CB2-B14A-65622FBEA0B4}"/>
+    <hyperlink ref="D44" r:id="rId34" xr:uid="{98A0C304-CAF0-41EF-B1EA-BF07537A4730}"/>
+    <hyperlink ref="D45" r:id="rId35" xr:uid="{A3E5F334-B5CE-4AEE-A42F-A5A17D96742A}"/>
+    <hyperlink ref="D36" r:id="rId36" xr:uid="{E447C236-D2AB-4A20-B7C1-8591FA3BE211}"/>
+    <hyperlink ref="D46" r:id="rId37" xr:uid="{6BB870EC-F64E-4BA7-8065-EB3402974981}"/>
+    <hyperlink ref="D37" r:id="rId38" xr:uid="{9D31C861-653F-4F2A-884C-44664722875D}"/>
+    <hyperlink ref="D47" r:id="rId39" xr:uid="{D3C33CAD-BAA3-447A-AF42-A156E65BC35D}"/>
+    <hyperlink ref="D35" r:id="rId40" xr:uid="{90D635D6-A4E8-4BE4-B7D4-67E3C59A2CEC}"/>
+    <hyperlink ref="D34" r:id="rId41" xr:uid="{50B70E74-0596-4624-AAA8-4F7F63D093DF}"/>
+    <hyperlink ref="D50" r:id="rId42" xr:uid="{B5312202-AB22-4CBA-AFB1-BA400ED0C6AD}"/>
+    <hyperlink ref="D49" r:id="rId43" xr:uid="{99DB107E-7511-46F5-A50B-F0E54A20B7BB}"/>
+    <hyperlink ref="D9" r:id="rId44" xr:uid="{DE11B2B4-25B0-47D6-BDD4-1773903E4FA2}"/>
+    <hyperlink ref="D22" r:id="rId45" xr:uid="{E8C63B3D-EDA3-432D-9AAB-D8AEE5906FA2}"/>
+    <hyperlink ref="D23" r:id="rId46" xr:uid="{2DAF0877-9D03-4B12-9B7F-FE41D0246E41}"/>
+    <hyperlink ref="D33" r:id="rId47" xr:uid="{320764C5-C57C-4E1C-A57A-4B57CFA56683}"/>
+    <hyperlink ref="D4" r:id="rId48" xr:uid="{04EFE255-94AD-416E-A2C7-6235F9601746}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId44"/>
+  <pageSetup orientation="portrait" r:id="rId49"/>
 </worksheet>
 </file>